--- a/downloads/loesungen/08_Sprachkurse_3NF_Loesung.xlsx
+++ b/downloads/loesungen/08_Sprachkurse_3NF_Loesung.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSON" sheetId="1" r:id="Re74efa7a1a9d4631"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABTEILUNG" sheetId="2" r:id="Rf97cdadef5944b4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPRACHKENNTNIS" sheetId="3" r:id="R21cc482e3935491c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSON" sheetId="1" r:id="Rc19853f081884a33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ABTEILUNG" sheetId="2" r:id="Rb89f531fa0614471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPRACHKENNTNIS" sheetId="3" r:id="R6d6928c72ab94ff4"/>
   </x:sheets>
 </x:workbook>
 </file>
